--- a/data/trans_orig/IMC_Medido-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Provincia-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores medido</t>
+          <t>Índice de masa corporal (IMC) medio de los menores medido (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +677,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,07; 19,71</t>
+          <t>18,15; 19,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,57; 19,12</t>
+          <t>17,55; 19,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,17; 20,1</t>
+          <t>17,17; 20,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,74; 21,47</t>
+          <t>18,71; 21,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,32; 20,34</t>
+          <t>18,31; 20,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,07; 18,85</t>
+          <t>17,11; 18,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,57; 20,15</t>
+          <t>18,65; 20,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,17; 19,5</t>
+          <t>18,24; 19,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,36; 19,06</t>
+          <t>17,42; 19,02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +787,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,54; 20,19</t>
+          <t>18,45; 20,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,78; 20,67</t>
+          <t>18,83; 20,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,7; 23,12</t>
+          <t>18,71; 23,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,89; 20,39</t>
+          <t>18,81; 20,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,47; 19,99</t>
+          <t>18,41; 20,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,35; 21,15</t>
+          <t>18,32; 21,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,91; 20,01</t>
+          <t>18,92; 20,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,83; 20,03</t>
+          <t>18,84; 20,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 22,03</t>
+          <t>18,99; 22,09</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,38; 19,99</t>
+          <t>18,52; 20,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,89; 19,28</t>
+          <t>17,82; 19,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,52; 21,07</t>
+          <t>17,61; 21,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,85; 20,6</t>
+          <t>18,84; 20,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,05; 19,84</t>
+          <t>18,06; 19,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,31; 22,25</t>
+          <t>19,31; 22,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,81; 20,03</t>
+          <t>18,85; 19,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,15; 19,27</t>
+          <t>18,15; 19,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,88; 20,92</t>
+          <t>18,83; 21,14</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,87; 20,0</t>
+          <t>17,86; 20,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,52; 20,48</t>
+          <t>18,5; 20,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,98; 20,39</t>
+          <t>17,12; 20,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,71; 20,72</t>
+          <t>18,67; 20,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,48; 20,66</t>
+          <t>18,44; 20,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 20,13</t>
+          <t>17,32; 20,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,57; 20,03</t>
+          <t>18,52; 19,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,71; 20,22</t>
+          <t>18,71; 20,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,53; 19,56</t>
+          <t>17,43; 19,59</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1117,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,56; 23,9</t>
+          <t>18,65; 24,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,55; 19,25</t>
+          <t>17,61; 19,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,95; 22,59</t>
+          <t>18,8; 22,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,77; 21,45</t>
+          <t>18,7; 21,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,07; 19,87</t>
+          <t>18,09; 19,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,44; 23,61</t>
+          <t>19,26; 23,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,93; 21,98</t>
+          <t>18,92; 22,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,03; 19,21</t>
+          <t>17,99; 19,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,45; 22,32</t>
+          <t>19,52; 22,33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1227,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,65; 20,5</t>
+          <t>18,63; 20,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,69; 19,37</t>
+          <t>17,73; 19,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,61; 19,75</t>
+          <t>17,6; 19,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,22; 19,93</t>
+          <t>18,21; 19,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,5; 20,7</t>
+          <t>18,43; 20,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,54; 20,97</t>
+          <t>18,5; 21,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,6; 19,92</t>
+          <t>18,66; 19,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,36; 19,75</t>
+          <t>18,39; 19,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,38; 20,16</t>
+          <t>18,46; 20,21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,65; 19,84</t>
+          <t>18,59; 19,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,58; 18,72</t>
+          <t>17,62; 18,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,85; 22,57</t>
+          <t>18,95; 22,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1357,27 +1357,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,72; 19,08</t>
+          <t>17,72; 19,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,33; 20,45</t>
+          <t>18,4; 20,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,88; 19,77</t>
+          <t>18,89; 19,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,78; 18,66</t>
+          <t>17,8; 18,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,94; 20,86</t>
+          <t>18,89; 20,85</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,63; 21,11</t>
+          <t>19,75; 21,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,54; 19,82</t>
+          <t>18,52; 19,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,58; 18,68</t>
+          <t>17,67; 18,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,14; 21,43</t>
+          <t>20,15; 21,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,6; 19,75</t>
+          <t>18,58; 19,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,94; 20,46</t>
+          <t>18,87; 20,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,07; 21,08</t>
+          <t>20,07; 21,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,51</t>
+          <t>18,68; 19,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,52; 19,55</t>
+          <t>18,49; 19,55</t>
         </is>
       </c>
     </row>
@@ -1557,32 +1557,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19,19; 19,89</t>
+          <t>19,18; 19,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,52; 19,07</t>
+          <t>18,5; 19,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,84; 20,67</t>
+          <t>18,79; 20,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,48; 20,09</t>
+          <t>19,45; 20,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,31</t>
+          <t>18,72; 19,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,06; 19,96</t>
+          <t>19,09; 19,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,08</t>
+          <t>18,68; 19,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,11; 20,09</t>
+          <t>19,08; 20,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Provincia-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores medido (tasa de respuesta: 78,69%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,15; 19,61</t>
+          <t>18,11; 19,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,55; 19,18</t>
+          <t>17,54; 19,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,17; 20,12</t>
+          <t>17,2; 20,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,71; 21,4</t>
+          <t>18,69; 21,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,31; 20,48</t>
+          <t>18,3; 20,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,11; 18,88</t>
+          <t>17,2; 18,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,65; 20,34</t>
+          <t>18,62; 20,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,24; 19,52</t>
+          <t>18,15; 19,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,42; 19,02</t>
+          <t>17,42; 19,15</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,45; 20,06</t>
+          <t>18,55; 20,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,83; 20,69</t>
+          <t>18,85; 20,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,71; 23,02</t>
+          <t>18,45; 22,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,81; 20,43</t>
+          <t>18,82; 20,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,41; 20,06</t>
+          <t>18,51; 20,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,32; 21,18</t>
+          <t>18,26; 21,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,92; 20,01</t>
+          <t>18,91; 20,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,84; 20,05</t>
+          <t>18,8; 20,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,99; 22,09</t>
+          <t>18,91; 22,16</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,52; 20,0</t>
+          <t>18,52; 20,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,82; 19,15</t>
+          <t>17,86; 19,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,61; 21,13</t>
+          <t>17,64; 21,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,84; 20,55</t>
+          <t>18,77; 20,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,06; 19,83</t>
+          <t>18,05; 19,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,31; 22,21</t>
+          <t>19,33; 22,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,85; 19,97</t>
+          <t>18,81; 20,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,15; 19,28</t>
+          <t>18,18; 19,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,83; 21,14</t>
+          <t>18,78; 21,13</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,86; 20,0</t>
+          <t>17,9; 19,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,5; 20,6</t>
+          <t>18,51; 20,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,12; 20,32</t>
+          <t>16,99; 20,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,67; 20,65</t>
+          <t>18,64; 20,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,44; 20,61</t>
+          <t>18,49; 20,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,32; 20,32</t>
+          <t>17,14; 20,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,52; 19,94</t>
+          <t>18,55; 20,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,71; 20,32</t>
+          <t>18,71; 20,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,43; 19,59</t>
+          <t>17,45; 19,69</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,65; 24,7</t>
+          <t>18,62; 24,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,61; 19,23</t>
+          <t>17,57; 19,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,8; 22,6</t>
+          <t>18,9; 22,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,7; 21,52</t>
+          <t>18,54; 21,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,09; 19,99</t>
+          <t>18,03; 19,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,26; 23,59</t>
+          <t>19,42; 23,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,92; 22,01</t>
+          <t>19,0; 22,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,99; 19,28</t>
+          <t>17,99; 19,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,52; 22,33</t>
+          <t>19,53; 22,23</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,63; 20,56</t>
+          <t>18,62; 20,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,73; 19,36</t>
+          <t>17,76; 19,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,6; 19,75</t>
+          <t>17,56; 19,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,21; 19,92</t>
+          <t>18,22; 20,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,43; 20,8</t>
+          <t>18,46; 20,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,5; 21,02</t>
+          <t>18,39; 20,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,66; 19,93</t>
+          <t>18,65; 19,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,39; 19,78</t>
+          <t>18,41; 19,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,46; 20,21</t>
+          <t>18,34; 20,14</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,59; 19,87</t>
+          <t>18,6; 19,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,62; 18,77</t>
+          <t>17,59; 18,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,95; 22,62</t>
+          <t>18,78; 22,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,86; 20,02</t>
+          <t>18,86; 20,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,72; 19,03</t>
+          <t>17,71; 19,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,4; 20,43</t>
+          <t>18,38; 20,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,89; 19,74</t>
+          <t>18,87; 19,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,8; 18,7</t>
+          <t>17,78; 18,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,89; 20,85</t>
+          <t>18,82; 20,8</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,75; 21,21</t>
+          <t>19,66; 21,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,52; 19,82</t>
+          <t>18,48; 19,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,67; 18,73</t>
+          <t>17,65; 18,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,15; 21,45</t>
+          <t>20,09; 21,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,58; 19,72</t>
+          <t>18,63; 19,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,87; 20,42</t>
+          <t>18,85; 20,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,07; 21,1</t>
+          <t>20,1; 21,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,48</t>
+          <t>18,66; 19,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,49; 19,55</t>
+          <t>18,5; 19,53</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19,18; 19,83</t>
+          <t>19,17; 19,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,04</t>
+          <t>18,5; 19,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,64</t>
+          <t>18,79; 20,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,45; 20,08</t>
+          <t>19,44; 20,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,72; 19,26</t>
+          <t>18,7; 19,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,09; 19,96</t>
+          <t>19,07; 20,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,42; 19,89</t>
+          <t>19,44; 19,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,09</t>
+          <t>18,68; 19,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,08; 20,13</t>
+          <t>19,1; 20,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Provincia-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19,66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19,22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18,15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>18,85</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>18,32</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18,31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,66</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,22</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,95</t>
+          <t>17,96</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18,11</t>
+          <t>18,06</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,11; 19,77</t>
+          <t>18,74; 21,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,54; 19,11</t>
+          <t>18,32; 20,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,2; 20,27</t>
+          <t>17,28; 19,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,69; 21,28</t>
+          <t>18,07; 19,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,3; 20,54</t>
+          <t>17,57; 19,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,2; 18,95</t>
+          <t>17,08; 19,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,62; 20,17</t>
+          <t>18,57; 20,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,15; 19,52</t>
+          <t>18,17; 19,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,42; 19,15</t>
+          <t>17,42; 18,83</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19,55</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19,14</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19,58</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>19,29</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>19,63</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>20,93</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,55</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,14</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,55</t>
+          <t>19,58</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20,34</t>
+          <t>19,58</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,55; 20,18</t>
+          <t>18,89; 20,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,85; 20,63</t>
+          <t>18,47; 19,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,45; 22,7</t>
+          <t>18,38; 21,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,82; 20,34</t>
+          <t>18,54; 20,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,51; 20,03</t>
+          <t>18,78; 20,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,26; 21,37</t>
+          <t>18,39; 21,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,91; 20,06</t>
+          <t>18,91; 20,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,8; 20,04</t>
+          <t>18,83; 20,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,91; 22,16</t>
+          <t>18,72; 20,91</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,82</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20,82</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>19,18</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>18,53</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18,82</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,55</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,82</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,68</t>
+          <t>18,87</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19,83</t>
+          <t>19,88</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,52; 20,1</t>
+          <t>18,85; 20,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,86; 19,21</t>
+          <t>18,05; 19,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,64; 21,16</t>
+          <t>19,57; 22,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,77; 20,57</t>
+          <t>18,38; 19,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,05; 19,78</t>
+          <t>17,89; 19,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,33; 22,26</t>
+          <t>17,54; 21,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,81; 20,04</t>
+          <t>18,81; 20,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,18; 19,28</t>
+          <t>18,15; 19,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,78; 21,13</t>
+          <t>18,91; 21,01</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,57</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19,55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18,62</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>18,72</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>19,4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18,35</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19,57</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,55</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,56</t>
+          <t>18,44</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18,45</t>
+          <t>18,53</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,9; 19,93</t>
+          <t>18,71; 20,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,51; 20,58</t>
+          <t>18,48; 20,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,99; 20,02</t>
+          <t>17,25; 20,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,64; 20,66</t>
+          <t>17,87; 20,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,49; 20,63</t>
+          <t>18,52; 20,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,14; 20,05</t>
+          <t>17,05; 20,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,55; 20,02</t>
+          <t>18,57; 20,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,71; 20,27</t>
+          <t>18,71; 20,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 19,69</t>
+          <t>17,53; 19,67</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19,77</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18,84</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20,75</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>20,17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>18,27</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>20,37</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19,77</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,84</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,79</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20,59</t>
+          <t>20,55</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,62; 24,39</t>
+          <t>18,77; 21,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,57; 19,17</t>
+          <t>18,07; 19,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,9; 22,48</t>
+          <t>19,44; 23,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,54; 21,16</t>
+          <t>18,56; 23,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,03; 19,83</t>
+          <t>17,55; 19,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,42; 23,66</t>
+          <t>18,88; 22,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,0; 22,27</t>
+          <t>18,93; 21,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,99; 19,32</t>
+          <t>18,03; 19,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,53; 22,23</t>
+          <t>19,41; 22,22</t>
         </is>
       </c>
     </row>
@@ -1174,47 +1174,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19,06</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19,54</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19,66</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>19,48</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>18,57</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18,61</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18,69</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19,26</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>19,06</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,54</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,67</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>19,26</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>19,06</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19,26</t>
+          <t>19,25</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,62; 20,59</t>
+          <t>18,22; 19,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,76; 19,4</t>
+          <t>18,5; 20,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,56; 19,75</t>
+          <t>18,52; 20,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,22; 20,0</t>
+          <t>18,65; 20,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,46; 20,72</t>
+          <t>17,69; 19,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,39; 20,84</t>
+          <t>17,7; 19,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,65; 19,89</t>
+          <t>18,6; 19,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,41; 19,75</t>
+          <t>18,36; 19,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,34; 20,14</t>
+          <t>18,39; 20,13</t>
         </is>
       </c>
     </row>
@@ -1284,39 +1284,39 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19,4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18,28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19,46</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>19,19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>18,11</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>20,28</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19,4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>18,28</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>19,86</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>19,3</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,3</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>18,2</t>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19,7</t>
+          <t>19,63</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,6; 19,86</t>
+          <t>18,86; 20,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,59; 18,69</t>
+          <t>17,72; 19,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,78; 22,47</t>
+          <t>18,49; 20,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,86; 20,03</t>
+          <t>18,65; 19,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,71; 19,01</t>
+          <t>17,58; 18,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,38; 20,53</t>
+          <t>18,66; 21,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,87; 19,79</t>
+          <t>18,88; 19,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,78; 18,62</t>
+          <t>17,78; 18,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,82; 20,8</t>
+          <t>18,92; 20,62</t>
         </is>
       </c>
     </row>
@@ -1394,47 +1394,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>20,73</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19,06</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19,66</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>20,39</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>19,01</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>18,14</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>20,73</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>18,2</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>20,56</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>19,04</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>19,06</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>19,59</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20,56</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19,04</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>19,0</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,66; 21,14</t>
+          <t>20,14; 21,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,48; 19,77</t>
+          <t>18,6; 19,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,65; 18,69</t>
+          <t>18,99; 20,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,09; 21,46</t>
+          <t>19,63; 21,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,63; 19,72</t>
+          <t>18,54; 19,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,85; 20,41</t>
+          <t>17,65; 18,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,1; 21,11</t>
+          <t>20,07; 21,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,66; 19,5</t>
+          <t>18,68; 19,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,53</t>
+          <t>18,59; 19,61</t>
         </is>
       </c>
     </row>
@@ -1504,32 +1504,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>19,78</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>18,98</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19,61</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>19,5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>18,77</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>19,47</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>18,98</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,49</t>
+          <t>19,03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>19,48</t>
+          <t>19,35</t>
         </is>
       </c>
     </row>
@@ -1557,37 +1557,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19,17; 19,86</t>
+          <t>19,48; 20,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,06</t>
+          <t>18,68; 19,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,66</t>
+          <t>19,19; 20,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,44; 20,08</t>
+          <t>19,19; 19,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,7; 19,31</t>
+          <t>18,52; 19,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,07; 20,01</t>
+          <t>18,6; 19,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,44; 19,87</t>
+          <t>19,42; 19,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,1; 20,12</t>
+          <t>19,02; 19,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Provincia-trans_orig.xlsx
@@ -528,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 81,88%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
